--- a/XlsData/Datas/#config.bullets.xlsx
+++ b/XlsData/Datas/#config.bullets.xlsx
@@ -90,14 +90,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -555,148 +548,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/XlsData/Datas/#config.bullets.xlsx
+++ b/XlsData/Datas/#config.bullets.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16660"/>
+    <workbookView windowWidth="26860" windowHeight="14500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <t>##var</t>
   </si>
@@ -41,6 +41,9 @@
     <t>desc</t>
   </si>
   <si>
+    <t>imageid</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -50,15 +53,6 @@
     <t>string</t>
   </si>
   <si>
-    <t>##group</t>
-  </si>
-  <si>
-    <t>c,s</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
     <t>##</t>
   </si>
   <si>
@@ -68,16 +62,34 @@
     <t>描述</t>
   </si>
   <si>
+    <t>子弹形象</t>
+  </si>
+  <si>
     <t>普通射击</t>
   </si>
   <si>
     <t>飞机会以一定的间隔发射子弹</t>
   </si>
   <si>
+    <t>Bullets</t>
+  </si>
+  <si>
     <t>跟踪导弹</t>
   </si>
   <si>
     <t>飞机会发射可跟踪的子弹</t>
+  </si>
+  <si>
+    <t>Missile</t>
+  </si>
+  <si>
+    <t>火力强攻</t>
+  </si>
+  <si>
+    <t>飞机会发射强力的子弹</t>
+  </si>
+  <si>
+    <t>Flameshot</t>
   </si>
 </sst>
 </file>
@@ -1016,14 +1028,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5" outlineLevelCol="3"/>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5" outlineLevelCol="4"/>
   <cols>
     <col min="3" max="3" width="9.57142857142857" customWidth="1"/>
     <col min="4" max="4" width="32.8839285714286" customWidth="1"/>
+    <col min="5" max="5" width="11.9107142857143" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1036,66 +1049,84 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1</v>
+    <row r="4" spans="1:5">
+      <c r="B4">
+        <v>1001</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:5">
       <c r="B5">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:5">
       <c r="B6">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>19</v>
+      </c>
+      <c r="E6" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/XlsData/Datas/#config.bullets.xlsx
+++ b/XlsData/Datas/#config.bullets.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
   <si>
     <t>##var</t>
   </si>
@@ -44,6 +44,12 @@
     <t>imageid</t>
   </si>
   <si>
+    <t>hurt</t>
+  </si>
+  <si>
+    <t>speed</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -63,6 +69,12 @@
   </si>
   <si>
     <t>子弹形象</t>
+  </si>
+  <si>
+    <t>伤害</t>
+  </si>
+  <si>
+    <t>速度</t>
   </si>
   <si>
     <t>普通射击</t>
@@ -1028,15 +1040,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5" outlineLevelCol="4"/>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="9.57142857142857" customWidth="1"/>
     <col min="4" max="4" width="32.8839285714286" customWidth="1"/>
     <col min="5" max="5" width="11.9107142857143" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1052,81 +1064,117 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:7">
       <c r="B4">
         <v>1001</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>18</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>360</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:7">
       <c r="B5">
         <v>1002</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>21</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>360</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:7">
       <c r="B6">
         <v>1003</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E6" t="s">
-        <v>20</v>
+        <v>24</v>
+      </c>
+      <c r="F6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>360</v>
       </c>
     </row>
   </sheetData>

--- a/XlsData/Datas/#config.bullets.xlsx
+++ b/XlsData/Datas/#config.bullets.xlsx
@@ -1154,7 +1154,7 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>360</v>
+        <v>240</v>
       </c>
     </row>
     <row r="6" spans="1:7">

--- a/XlsData/Datas/#config.bullets.xlsx
+++ b/XlsData/Datas/#config.bullets.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
   <si>
     <t>##var</t>
   </si>
@@ -50,6 +50,9 @@
     <t>speed</t>
   </si>
   <si>
+    <t>type</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -75,6 +78,9 @@
   </si>
   <si>
     <t>速度</t>
+  </si>
+  <si>
+    <t>类型</t>
   </si>
   <si>
     <t>普通射击</t>
@@ -1040,15 +1046,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5" outlineLevelCol="6"/>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5" outlineLevelCol="7"/>
   <cols>
     <col min="3" max="3" width="9.57142857142857" customWidth="1"/>
     <col min="4" max="4" width="32.8839285714286" customWidth="1"/>
     <col min="5" max="5" width="11.9107142857143" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1070,65 +1076,74 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
+      <c r="G2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="H2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" t="s">
-        <v>8</v>
-      </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="H3" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:8">
       <c r="B4">
         <v>1001</v>
       </c>
       <c r="C4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1136,19 +1151,22 @@
       <c r="G4">
         <v>360</v>
       </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:8">
       <c r="B5">
         <v>1002</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -1156,25 +1174,31 @@
       <c r="G5">
         <v>240</v>
       </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:8">
       <c r="B6">
         <v>1003</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F6">
         <v>2</v>
       </c>
       <c r="G6">
         <v>360</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/XlsData/Datas/#config.bullets.xlsx
+++ b/XlsData/Datas/#config.bullets.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
   <si>
     <t>##var</t>
   </si>
@@ -53,6 +53,9 @@
     <t>type</t>
   </si>
   <si>
+    <t>interval</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -62,6 +65,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>float</t>
+  </si>
+  <si>
     <t>##</t>
   </si>
   <si>
@@ -81,6 +87,9 @@
   </si>
   <si>
     <t>类型</t>
+  </si>
+  <si>
+    <t>触发间隔</t>
   </si>
   <si>
     <t>普通射击</t>
@@ -1046,15 +1055,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5" outlineLevelCol="7"/>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5"/>
   <cols>
     <col min="3" max="3" width="9.57142857142857" customWidth="1"/>
     <col min="4" max="4" width="32.8839285714286" customWidth="1"/>
     <col min="5" max="5" width="11.9107142857143" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1079,71 +1088,80 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="G2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
+      <c r="H2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" t="s">
-        <v>9</v>
+      <c r="I2" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H3" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="I3" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:9">
       <c r="B4">
         <v>1001</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F4">
         <v>1</v>
@@ -1154,19 +1172,22 @@
       <c r="H4">
         <v>1</v>
       </c>
+      <c r="I4">
+        <v>0.2</v>
+      </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:9">
       <c r="B5">
         <v>1002</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -1177,19 +1198,22 @@
       <c r="H5">
         <v>2</v>
       </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:9">
       <c r="B6">
         <v>1003</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F6">
         <v>2</v>
@@ -1199,6 +1223,9 @@
       </c>
       <c r="H6">
         <v>1</v>
+      </c>
+      <c r="I6">
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>
